--- a/docs/TechnicalSpec.xlsx
+++ b/docs/TechnicalSpec.xlsx
@@ -5,10 +5,11 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Technical Details" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Estimates" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
   <si>
     <t xml:space="preserve">Solution</t>
   </si>
@@ -248,6 +249,183 @@
   </si>
   <si>
     <t xml:space="preserve">Initial setup takes effort, but avoids manual cloud configuration risk later.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workstream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What Will Be Built</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimate Days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimate Hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PoV scope confirmation &amp; technical design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirm PoV journey, success criteria, CSV fields, quote fields, backend modules, DB schema and API approach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Includes bank stakeholder alignment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP lean environment setup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Run, Cloud SQL PostgreSQL, Cloud Storage, Secret Manager, Cloud Logging and basic IAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lean setup only, not full production architecture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Codebase and deployment setup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full-stack repo, backend scaffold, frontend connection structure, environment configuration and basic deployment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent-assisted coding can speed this up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Database schema build</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tables for vehicles, imports, quote requests, quote responses, saved vehicles, user events and audit logs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simple but traceable schema</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSV upload and vehicle import</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSV upload, file storage, row validation, vehicle loading, failed row/error reporting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main inventory path for Lean PoV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle catalogue backend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle search, filters, details, availability status and basic pagination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Core user journey functionality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEX LVS adapter shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API-ready adapter structure, sample/mock response mapping, fallback handling if API access is delayed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live API integration depends on access and documentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blackhorse quote adapter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quote request structure, sandbox/mock quote call, response mapping, quote status and expiry handling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Highest external dependency risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Session and saved vehicle logic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anonymous session handling, saved vehicle list, retrieve saved vehicles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avoids full login/SSO for PoV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frontend-backend connection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connect existing/basic UI to vehicle list, detail, save, quote and CSV upload APIs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI/UX design excluded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Behaviour event tracking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capture search, view, save, quote requested, quote generated and drop-off events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required for hypothesis validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Audit, logging and error handling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSV errors, API errors, quote failures, audit logs and technical error logs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum bank-facing traceability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security basics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secret Manager usage, masked logs, no secrets in code, basic IAM and environment separation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lean security controls only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Testing and fixes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSV tests, API tests, quote journey tests, frontend journey testing and defect fixes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Includes agent-generated code validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demo preparation and handover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demo data, walkthrough notes, known limitations, setup guide and next-phase recommendation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needed for stakeholder playback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank/stakeholder buffer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Access delays, compliance questions, closed-loop feedback, stakeholder review and minor rework</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4–5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32–40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank-realistic delivery buffer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Bank-realistic Lean Estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49–50 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">392–400 hours</t>
   </si>
 </sst>
 </file>
@@ -257,11 +435,12 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -283,11 +462,20 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -338,21 +526,53 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -481,272 +701,272 @@
   <dimension ref="A1:D19"/>
   <sheetFormatPr defaultColWidth="56.48046875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="41.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="41.88"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+    <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+    <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+    <row r="13" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="4" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+    <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="4" t="s">
         <v>75</v>
       </c>
     </row>
@@ -759,4 +979,383 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultColWidth="50.36328125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="8.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="5" width="17.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="5" width="18.78"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9"/>
+      <c r="B18" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="C18" s="11"/>
+      <c r="D18" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F18" s="11"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>